--- a/v3/CS0006/CS0006_ReadingQuiz.xlsx
+++ b/v3/CS0006/CS0006_ReadingQuiz.xlsx
@@ -3340,17 +3340,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>SC18</t>
+          <t>SC09</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CS0006_SC18_I.webp</t>
+          <t>CS0006_SC09_I.webp</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>SC18</t>
+          <t>SC09</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>["mouse.", "the", "on", "jumped", "Cat", "The"]</t>
+          <t>["a stone.", "under", "clothes", "his", "hid", "The Cat"]</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>["The", "Cat", "jumped", "on", "the", "mouse."]</t>
+          <t>["The Cat", "hid", "his", "clothes", "under", "a stone."]</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -3457,7 +3457,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>The</t>
+          <t>The Cat</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
@@ -3483,7 +3483,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>hid</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
@@ -3509,7 +3509,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>jumped</t>
+          <t>his</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -3535,7 +3535,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>on</t>
+          <t>clothes</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
@@ -3561,7 +3561,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>under</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -3587,7 +3587,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>mouse.</t>
+          <t>a stone.</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
